--- a/docs/keyword-serp-tracker-2026-08.xlsx
+++ b/docs/keyword-serp-tracker-2026-08.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERP영역분석" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="후보키워드전체" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="실행플랜" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="네이버광고실측" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -119,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -173,6 +174,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1451,7 +1461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1556,9 +1566,9 @@
           <t>케이크토퍼 카테고리 고정, 블로그는 가십 경쟁 심함</t>
         </is>
       </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>검색량 0에 가까움(PC&lt;10,모바일&lt;10), 경쟁낮음, 광고주0 — 조합형 실패</t>
         </is>
       </c>
     </row>
@@ -1598,9 +1608,9 @@
           <t>킨더조이 인형꽃다발과 카테고리 겹침 — 상품명 최적화 시도</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>검색량 0에 가까움(PC&lt;10,모바일&lt;10), 경쟁낮음, 광고주0 — 조합형 실패</t>
         </is>
       </c>
     </row>
@@ -1640,9 +1650,9 @@
           <t>★진짜 꽃다발 카테고리 열림. 최우선 실행 대상★</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>검색량 0에 가까움(PC&lt;10,모바일&lt;10), 경쟁낮음, 광고주0</t>
         </is>
       </c>
     </row>
@@ -1724,9 +1734,9 @@
           <t>선물샵 캐러셀 미검출, 대신 경쟁 꽃집 해시태그 블로그 다수 확인</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>검색량 0에 가까움(PC&lt;10,모바일&lt;10), 경쟁높음, 광고주8, PC클릭률1.79%</t>
         </is>
       </c>
     </row>
@@ -1762,9 +1772,9 @@
           <t>중학교/대학과 같은 패턴(열림) 예상</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>검색량 0에 가까움(PC&lt;10,모바일&lt;10), 경쟁높음, 광고주8(볼륨없이 이미 포화)</t>
         </is>
       </c>
     </row>
@@ -1804,9 +1814,9 @@
           <t>★진짜 꽃다발 카테고리 열림. 학교급 나열형 상품명 벤치마킹★</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>PC20+모바일110=130/월, 경쟁높음, 광고주8 — Tier A 중 유일하게 유의미한 볼륨</t>
         </is>
       </c>
     </row>
@@ -1842,9 +1852,9 @@
           <t>이미 상품명에 있음, 낮은 우선순위</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>PC&lt;10+모바일10=10, 경쟁높음, 광고주8</t>
         </is>
       </c>
     </row>
@@ -2062,9 +2072,9 @@
           <t>중학교/대학과 같은 패턴(열림) 예상</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>검색량 0에 가까움(PC&lt;10,모바일&lt;10), 경쟁높음, 광고주10(볼륨없이 이미 포화)</t>
         </is>
       </c>
     </row>
@@ -2146,9 +2156,9 @@
           <t>답변이 전부 고가선물(가방·가전·주얼리), 꽃 언급 0건 — 각도 신중 필요</t>
         </is>
       </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>근사치 '어머니칠순선물' PC20+모바일80=100/월, 경쟁높음, 광고주10, 클릭률1.43%/2.64%</t>
         </is>
       </c>
     </row>
@@ -2188,9 +2198,9 @@
           <t>지역꽃집 블로그 마케팅 활발 — 전국택배 각도로 차별화 필요</t>
         </is>
       </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>PC10+모바일10=20/월, 경쟁높음, 광고주10</t>
         </is>
       </c>
     </row>
@@ -2226,9 +2236,9 @@
           <t>볼륨 낮음, 우선순위 낮음</t>
         </is>
       </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>근사치 '부모님환갑선물' PC130+모바일360=490/월, 경쟁높음, 광고주10 — 상품군은 다르나 수요 확인</t>
         </is>
       </c>
     </row>
@@ -2260,9 +2270,9 @@
       </c>
       <c r="F23" s="12" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>미실시</t>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>근사치 '부모님결혼기념일' PC20+모바일240=260/월, 경쟁높음, 광고주10</t>
         </is>
       </c>
     </row>
@@ -2570,6 +2580,7 @@
         </is>
       </c>
     </row>
+    <row r="32"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -2788,4 +2799,1456 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>네이버 검색광고 키워드도구 실측 (2026-08-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ 사용자가 '11월/12월/1월 시즌'으로 나눠 다운받았으나, 졸업 관련 키워드 수치가 3개 파일에서 완전히 동일 — 네이버 키워드도구는 특정 월 이력을 보여주지 않고 조회 시점(2026-08-19) 기준 스냅샷만 제공한다. 파일명의 '시즌' 구분은 실제 계절별 데이터가 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>키워드</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>PC검색수</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>모바일검색수</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>경쟁정도</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>노출광고수</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>① 후보 재확인 — 조합형(관계어+행사+꽃다발)은 검색량 0</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>아들졸업식꽃다발</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>리뷰엔 '아들+졸업식' 137건 있지만 이 조합을 그대로 검색하진 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="12" t="inlineStr"/>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>딸졸업식꽃다발</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>동일 패턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="12" t="inlineStr"/>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>중학교졸업식꽃다발</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="12" t="inlineStr"/>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>초등학교졸업식꽃다발</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>볼륨 없는데 광고주 8곳 — 정확타겟팅 아닌 넓은 매칭으로 걸림</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>고등학교졸업식꽃다발</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>동일 패턴, 광고주 더 많음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="12" t="inlineStr"/>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>입학식꽃다발</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>PC클릭률 1.79%(표본 작아 불안정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>② 실제 볼륨 있는 상위 카테고리어</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>졸업식꽃다발</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>2,680</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>3,170</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>가장 큰 헤드텀. 클릭률 낮음(0.65%/1.75%) — 쇼핑·정보성에 눌림</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="12" t="inlineStr"/>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>대학교졸업식꽃다발</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Tier A 학교급 중 유일하게 유의미</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="12" t="inlineStr"/>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>대학졸업식꽃다발</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>'대학교'보다 '대학'이 검색량 더 큼</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>졸업꽃다발(축약형)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>'졸업식'보다 짧은 형태도 상당한 볼륨</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>③ 완전 신규 발견 — 후보 리스트에 없었음</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>재롱잔치꽃다발</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>2,060</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>2,080</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>★모바일 볼륨 압도적. 인형꽃다발 라인 occasion과 정확히 일치하는데 후보에 없었음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="12" t="inlineStr"/>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>수료식꽃다발</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>1,070</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>1,160</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>졸업식과 다른 행사(유치원/학원 수료식). 신규 타겟</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="12" t="inlineStr"/>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>킨더조이꽃다발</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>★상품명과 정확히 일치. 킨더조이 레보니 인형꽃다발 라인 직결</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="12" t="inlineStr"/>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>졸업식인형꽃다발</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>볼륨 작지만 우리 상품군과 정확히 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>④ 퇴사·퇴직 클러스터 — 신규 발견</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>퇴사꽃다발</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>토픽풀에 없던 신규 군집. 4개 합쳐 400+/월</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="12" t="inlineStr"/>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>퇴직꽃다발</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="12" t="inlineStr"/>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>은퇴꽃다발</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>&lt;10</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="12" t="inlineStr"/>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>퇴임꽃다발</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>⑤ 결혼기념일 클러스터 — 파이는 크지만 희석됨</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>결혼기념일선물</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>4,070</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>최대 볼륨이지만 클릭률 0.25%/0.83% — 식당·주얼리 등과 섞여 희석</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="12" t="inlineStr"/>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>결혼기념일</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>1,870</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>동일 문제</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="12" t="inlineStr"/>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>결혼기념일이벤트</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>780</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="12" t="inlineStr"/>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>결혼기념일꽃</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>상품 특정형은 작지만 경쟁 '중간'이라 상대적으로 유리</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="12" t="inlineStr"/>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>결혼기념일꽃다발</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>정확 상품명은 오히려 작음</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>⑥ 브랜드 톤 판단 대기 항목 — 실측 수치 확보</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>성묘꽃다발</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>keyword-landscape 문서가 지적했던 추모시장. 이제 실제 볼륨 확보(190/월)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>⑦ 우리 제품군 핵심 키워드 — 건강하게 확인됨</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>프리저브드플라워</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>1,080</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>4,950</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>6,030</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>경쟁 '중간'인 게 핵심 — 높음 아닌 몇 안 되는 헤드텀</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="12" t="inlineStr"/>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>비누꽃다발</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>1,850</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>2,190</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>클릭률 1.66%/3.69% — 준수함</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="12" t="inlineStr"/>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>수국꽃다발</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>1,690</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>1,970</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>수국 꽃다발 라인과 정확 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="12" t="inlineStr"/>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>생일꽃다발</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>3,820</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>모바일 클릭률 6.04% — 이례적으로 높음</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="12" t="inlineStr"/>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>프리지아꽃다발</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>졸업식 대표꽃 topic-pool #11과 연결</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="12" t="inlineStr"/>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>비누꽃한송이</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>'비누꽃 한송이·두송이 박스' 라인과 정확 일치, 클릭률 1.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>⑧ 미취급 소재 — 시장 신호만(참고용)</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>작약꽃다발</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>현재 라인업에 없는 소재. 검토 가치는 있으나 이번 결정 대상 아님</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="12" t="inlineStr"/>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>튤립꽃다발</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="12" t="inlineStr"/>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>목화꽃다발</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="F37" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>⑨ 가격대 검색 패턴</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>꽃다발2만원</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>2만원대 &gt; 3만원대 &gt; 5만원대 순으로 검색</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="42" customHeight="1">
+      <c r="A39" s="12" t="inlineStr"/>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>꽃다발3만원</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E39" s="12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="12" t="inlineStr"/>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>꽃다발5만원</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>